--- a/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
+++ b/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
   <si>
     <t>特性</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,6 +167,254 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>数据修改操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新update/upsert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、各参数项校验（参考校验规则）
+2、其他测试点可和insert合并
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、参数校验（可组合其他查询条件覆盖）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找find/findOne</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、涉及参数进行参数项校验测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数项校验测试（涉及json对象可以考虑在某项参数校验中统一测试）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>findandmodify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>findandremove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引index（创建、查询、删除）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、参数校验（可组合其他查询条件）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上传put、查询get、删除delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本数据操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表挂载操作attach/deattach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除remove/truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、文件类型（考虑所有类型）
+3、文件大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、参数校验
+2、attach结合分区范围验证切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split/splitAsync</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、参数校验
+2、结合createCL中相关参数组合测试边界和特定类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、和相关业务组合特定值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建create</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询get、删除drop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create，drop，alter，list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询、删除、启动、停止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、和相关业务组合特定值
+3、相互约束条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、和相关业务组合特定值
+3、创建data节点需要考虑数据库配置参数
+4、节点配置文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置文件校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setSessionAttr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志路径logpath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志文件大小logfilesz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志内存页面数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志同步最大并发数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志缓存块大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数校验（重点考虑边界值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、覆盖涉及参数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">1、各参数项校验（参考校验规则）
 2、记录类型（考虑所有文档类型）
 3、记录大小（可组合记录类型涉及）
@@ -174,125 +422,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据修改操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新update/upsert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、各参数项校验（参考校验规则）
-2、其他测试点可和insert合并
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、参数校验（可组合其他查询条件覆盖）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查找find/findOne</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、涉及参数进行参数项校验测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数项校验测试（涉及json对象可以考虑在某项参数校验中统一测试）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>findandmodify</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>findandremove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引index（创建、查询、删除）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、参数校验（可组合其他查询条件）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上传put、查询get、删除delete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本数据操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表挂载操作attach/deattach</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除remove/truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、各参数项校验（参考校验规则）
-2、文件类型（考虑所有类型）
-3、文件大小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、参数校验
-2、attach结合分区范围验证切分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>split/splitAsync</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、参数校验
-2、结合createCL中相关参数组合测试边界和特定类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CS管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CL管理</t>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -301,147 +443,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建create</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询get、删除drop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create，drop，alter，list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询、删除、启动、停止</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、各参数项校验（参考校验规则）
-2、和相关业务组合特定值
-3、相互约束条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、各参数项校验（参考校验规则）
-2、和相关业务组合特定值
-3、创建data节点需要考虑数据库配置参数
-4、节点配置文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置文件校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>setSessionAttr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志路径logpath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志文件大小logfilesz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志内存页面数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志同步最大并发数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步策略</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志缓存块大小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数校验（重点考虑边界值）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、覆盖涉及参数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、各参数项校验（参考校验规则）
 2、记录类型（考虑所有文档类型）
-3、记录大小（可组合记录类型涉及）
-</t>
+3、记录大小（可组合记录类型涉及）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -570,80 +578,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -655,7 +598,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -935,11 +878,11 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="39" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="77.25" customWidth="1"/>
+    <col min="5" max="5" width="51.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -950,13 +893,13 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="8" customFormat="1" ht="27">
@@ -971,13 +914,13 @@
         <v>12</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="54">
@@ -987,13 +930,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
@@ -1001,29 +944,29 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="8" customFormat="1">
@@ -1032,19 +975,19 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1052,7 +995,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -1061,7 +1004,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1070,7 +1013,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -1079,7 +1022,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -1088,7 +1031,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -1097,7 +1040,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -1105,14 +1048,14 @@
       <c r="A13" s="5"/>
       <c r="B13" s="2"/>
       <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:7" s="8" customFormat="1" ht="20.25" customHeight="1">
+    <row r="14" spans="1:7" s="8" customFormat="1" ht="28.5" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>3</v>
       </c>
@@ -1120,32 +1063,32 @@
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="3"/>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" customHeight="1">
@@ -1153,7 +1096,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -1161,13 +1104,13 @@
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1">
@@ -1175,7 +1118,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -1183,200 +1126,200 @@
       <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="E19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42" customHeight="1">
       <c r="A20" s="4"/>
-      <c r="B20" s="11"/>
+      <c r="B20" s="12"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
-      <c r="B21" s="11"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
-      <c r="B22" s="11"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4"/>
-      <c r="B23" s="11"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4"/>
-      <c r="B24" s="11"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1"/>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1">
       <c r="A25" s="4"/>
-      <c r="B25" s="11"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4"/>
-      <c r="B26" s="11"/>
+      <c r="B26" s="12"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3"/>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4"/>
-      <c r="B27" s="11"/>
+      <c r="B27" s="12"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4"/>
-      <c r="B28" s="11"/>
+      <c r="B28" s="12"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="G28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4"/>
-      <c r="B29" s="11"/>
+      <c r="B29" s="12"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="27" customHeight="1">
       <c r="A30" s="4"/>
-      <c r="B30" s="11"/>
+      <c r="B30" s="12"/>
       <c r="C30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4"/>
-      <c r="B31" s="11"/>
+      <c r="B31" s="12"/>
       <c r="C31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:7" ht="27">
       <c r="A32" s="4"/>
-      <c r="B32" s="11"/>
+      <c r="B32" s="12"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1391,22 +1334,22 @@
         <v>7</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="F34" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
+++ b/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
@@ -179,12 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、各参数项校验（参考校验规则）
-2、其他测试点可和insert合并
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数据查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -213,10 +207,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>参数项校验测试（涉及json对象可以考虑在某项参数校验中统一测试）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>findandmodify</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -226,10 +216,6 @@
   </si>
   <si>
     <t>索引index（创建、查询、删除）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、参数校验（可组合其他查询条件）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -272,11 +258,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、参数校验
-2、结合createCL中相关参数组合测试边界和特定类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>domain管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,6 +298,139 @@
     <t>1、各参数项校验（参考校验规则）
 2、和相关业务组合特定值
 3、相互约束条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置文件校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setSessionAttr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志路径logpath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志文件大小logfilesz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步日志数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志内存页面数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志同步最大并发数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志缓存块大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数校验（重点考虑边界值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、覆盖涉及参数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、和相关业务组合特定值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、记录类型（考虑所有文档类型）
+3、记录大小（可组合记录类型涉及）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数项校验测试（涉及json对象可以考虑在某项参数校验中统一测试）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、其他测试点可和insert合并</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、和相关业务组合特定值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -327,129 +441,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cm管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置文件校验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>setSessionAttr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志路径logpath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志文件大小logfilesz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步日志数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志内存页面数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志同步最大并发数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步策略</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志缓存块大小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数校验（重点考虑边界值）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、覆盖涉及参数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、各参数项校验（参考校验规则）
-2、记录类型（考虑所有文档类型）
-3、记录大小（可组合记录类型涉及）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、各参数项校验（参考校验规则）
-2、和相关业务组合特定值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、各参数项校验（参考校验规则）
-2、记录类型（考虑所有文档类型）
-3、记录大小（可组合记录类型涉及）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
+    <t>1、参数校验（可组合其他查询条件）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、参数校验
+2、结合createCL中相关参数组合测试边界和特定类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -893,13 +890,13 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="8" customFormat="1" ht="27">
@@ -914,13 +911,13 @@
         <v>12</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="54">
@@ -930,13 +927,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
@@ -944,29 +941,29 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="8" customFormat="1">
@@ -975,19 +972,19 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -995,7 +992,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -1004,7 +1001,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1013,7 +1010,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -1022,7 +1019,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -1031,7 +1028,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -1040,7 +1037,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -1048,10 +1045,10 @@
       <c r="A13" s="5"/>
       <c r="B13" s="2"/>
       <c r="C13" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -1063,32 +1060,32 @@
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" customHeight="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29.25" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="3"/>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" customHeight="1">
@@ -1096,21 +1093,21 @@
       <c r="B16" s="3"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="16.5" customHeight="1">
+    <row r="17" spans="1:7" ht="40.5" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1">
@@ -1118,11 +1115,11 @@
       <c r="B18" s="3"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:7" s="8" customFormat="1" ht="44.25" customHeight="1">
+    <row r="19" spans="1:7" s="8" customFormat="1" ht="43.5" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
@@ -1136,13 +1133,13 @@
         <v>15</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="42" customHeight="1">
@@ -1153,40 +1150,40 @@
         <v>16</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="29.25" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="12"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="12"/>
       <c r="C22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1194,13 +1191,13 @@
       <c r="B23" s="12"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1208,25 +1205,25 @@
       <c r="B24" s="12"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1"/>
       <c r="G24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.5" customHeight="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.5" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="12"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1234,11 +1231,11 @@
       <c r="B26" s="12"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" s="3"/>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1246,11 +1243,11 @@
       <c r="B27" s="12"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1258,13 +1255,13 @@
       <c r="B28" s="12"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1272,29 +1269,29 @@
       <c r="B29" s="12"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="27" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="12"/>
       <c r="C30" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1304,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -1313,13 +1310,13 @@
       <c r="B32" s="12"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1334,22 +1331,22 @@
         <v>7</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
+++ b/internal_doc/05.测试设计/参数校验/子特性列表_参数校验.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
   <si>
     <t>特性</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -405,11 +405,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、各参数项校验（参考校验规则）
-2、和相关业务组合特定值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黄晓妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -447,6 +442,16 @@
   <si>
     <t>1、参数校验
 2、结合createCL中相关参数组合测试边界和特定类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、各参数项校验（参考校验规则）
+2、记录类型（考虑所有文档类型）
+3、记录大小（可组合记录类型涉及）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务管理（启动和停止）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -554,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -578,12 +583,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -595,7 +669,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -872,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -930,7 +1004,7 @@
         <v>43</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
         <v>70</v>
@@ -944,7 +1018,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
         <v>70</v>
@@ -962,46 +1036,45 @@
       <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="8" customFormat="1">
-      <c r="A6" s="9" t="s">
+    <row r="7" spans="1:7" s="8" customFormat="1">
+      <c r="A7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="5"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1010,7 +1083,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -1019,7 +1092,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -1028,7 +1101,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -1037,164 +1110,159 @@
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="5"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" s="8" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A14" s="9" t="s">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" s="8" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A15" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="E15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" customHeight="1">
+    <row r="16" spans="1:7" ht="29.25" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" ht="40.5" customHeight="1">
+        <v>40</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.5" customHeight="1">
+        <v>41</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" ht="40.5" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="D18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" s="8" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" s="8" customFormat="1" ht="43.5" customHeight="1">
+      <c r="A20" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B20" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="E20" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="42" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29.25" customHeight="1">
+    <row r="21" spans="1:7" ht="42" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="12"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="29.25" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="12"/>
-      <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="G22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="12"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
         <v>71</v>
@@ -1205,35 +1273,37 @@
       <c r="B24" s="12"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="G24" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="28.5" customHeight="1">
+    <row r="25" spans="1:7">
       <c r="A25" s="4"/>
       <c r="B25" s="12"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>75</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E25" s="1"/>
       <c r="G25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="28.5" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="12"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="G26" t="s">
         <v>71</v>
       </c>
@@ -1243,7 +1313,7 @@
       <c r="B27" s="12"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" t="s">
@@ -1255,11 +1325,9 @@
       <c r="B28" s="12"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>79</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E28" s="3"/>
       <c r="G28" t="s">
         <v>71</v>
       </c>
@@ -1269,89 +1337,103 @@
       <c r="B29" s="12"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>62</v>
+        <v>26</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="G29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="27" customHeight="1">
+    <row r="30" spans="1:7">
       <c r="A30" s="4"/>
       <c r="B30" s="12"/>
-      <c r="C30" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="27" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="12"/>
       <c r="C31" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" ht="27">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="12"/>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" ht="27">
+      <c r="A33" s="4"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G33" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="4"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" s="8" customFormat="1" ht="27">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" s="4"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" s="8" customFormat="1" ht="27">
+      <c r="A35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F34" s="8" t="s">
+      <c r="E35" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B19:B32"/>
+    <mergeCell ref="B20:B33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
